--- a/xlsx/country_comparison/top_tax_affected_share_various.xlsx
+++ b/xlsx/country_comparison/top_tax_affected_share_various.xlsx
@@ -53,21 +53,21 @@
     <t xml:space="preserve">USA</t>
   </si>
   <si>
-    <t xml:space="preserve">Supports tax on world top income to finance global poverty reduction
+    <t xml:space="preserve">Accepts tax on world top income to finance global poverty reduction
 (Any variant)</t>
   </si>
   <si>
     <t xml:space="preserve">Affected by the top tax (any variant)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supports tax on world top 1% to finance global poverty reduction
+    <t xml:space="preserve">Accepts tax on world top 1% to finance global poverty reduction
 (Additional 15% tax on income over [$120k/year in PPP])</t>
   </si>
   <si>
     <t xml:space="preserve">Affected by the top 1% tax (income &gt; $PPP 120k)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supports tax on world top 3% to finance global poverty reduction
+    <t xml:space="preserve">Accepts tax on world top 3% to finance global poverty reduction
 (Additional 15% tax over [$80k], 30% over [$120k], 45% over [$1M])</t>
   </si>
   <si>
